--- a/filer/22460218_torm.xlsx
+++ b/filer/22460218_torm.xlsx
@@ -7009,7 +7009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7149,20 +7149,20 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentOfFinancialAssets</t>
+          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentOfFinancialAssets</t>
+          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n">
-        <v>6854</v>
+        <v>-104</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>-4603</v>
+        <v>153</v>
       </c>
       <c r="G5" s="35" t="n">
         <v>0</v>
@@ -7182,25 +7182,27 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
+          <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
+          <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
       <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n">
-        <v>-104</v>
+        <v>1473</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="38" t="n"/>
+        <v>76</v>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>76</v>
+      </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7215,26 +7217,26 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermParticipatingInterests</t>
+          <t>fsa:LongtermTaxPayables</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermParticipatingInterests</t>
+          <t>fsa:LongtermTaxPayables</t>
         </is>
       </c>
       <c r="D7" s="35" t="n"/>
       <c r="E7" s="35" t="n">
-        <v>1473</v>
+        <v>45176</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>76</v>
+        <v>45176</v>
       </c>
       <c r="G7" s="35" t="n">
-        <v>76</v>
+        <v>45176</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>76</v>
+        <v>45176</v>
       </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
@@ -7250,92 +7252,28 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermTaxPayables</t>
+          <t>fsa:Ships</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermTaxPayables</t>
+          <t>fsa:Ships</t>
         </is>
       </c>
       <c r="D8" s="38" t="n"/>
       <c r="E8" s="38" t="n">
-        <v>45176</v>
+        <v>1643951</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>45176</v>
+        <v>1614144</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>45176</v>
+        <v>1693485</v>
       </c>
       <c r="H8" s="38" t="n">
-        <v>45176</v>
+        <v>1629904</v>
       </c>
       <c r="I8" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:OtherInvestmentAssets</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:OtherInvestmentAssets</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>1040654</v>
-      </c>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n"/>
-      <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
-      <c r="I9" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>fsa:Ships</t>
-        </is>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>fsa:Ships</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n">
-        <v>1643951</v>
-      </c>
-      <c r="F10" s="38" t="n">
-        <v>1614144</v>
-      </c>
-      <c r="G10" s="38" t="n">
-        <v>1693485</v>
-      </c>
-      <c r="H10" s="38" t="n">
-        <v>1629904</v>
-      </c>
-      <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/22460218_torm.xlsx
+++ b/filer/22460218_torm.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.USD)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse t.kr.</t>
+          <t>Resultatopgørelse t.USD</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -1431,7 +1431,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>AKTIVER t.kr.</t>
+          <t>AKTIVER t.USD</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
@@ -2621,7 +2621,7 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PASSIVER t.kr.</t>
+          <t>PASSIVER t.USD</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
@@ -4462,7 +4462,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse &amp; nøgleoplysninger (t.kr.)</t>
+          <t>Resultatopgørelse &amp; nøgleoplysninger (t.USD)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -4846,7 +4846,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Balance (t.kr.)</t>
+          <t>Balance (t.USD)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -6858,15 +6858,15 @@
         </is>
       </c>
       <c r="B60" s="29">
-        <f>IF('balance_raw_22460218'!$F$25="","—",IF(ABS(B20-'balance_raw_22460218'!$F$25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_22460218'!$F$25,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_22460218'!$F$25="","—",IF(ABS(B20-'balance_raw_22460218'!$F$25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-'balance_raw_22460218'!$F$25,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C60" s="29">
-        <f>IF('balance_raw_22460218'!$E$25="","—",IF(ABS(C20-'balance_raw_22460218'!$E$25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_22460218'!$E$25,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_22460218'!$E$25="","—",IF(ABS(C20-'balance_raw_22460218'!$E$25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-'balance_raw_22460218'!$E$25,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D60" s="29">
-        <f>IF('balance_raw_22460218'!$D$25="","—",IF(ABS(D20-'balance_raw_22460218'!$D$25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_22460218'!$D$25,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_22460218'!$D$25="","—",IF(ABS(D20-'balance_raw_22460218'!$D$25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-'balance_raw_22460218'!$D$25,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F60" s="25" t="inlineStr">
@@ -6882,15 +6882,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_22460218'!$F$53="","—",IF(ABS(B24-'balance_raw_22460218'!$F$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_22460218'!$F$53,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_22460218'!$F$53="","—",IF(ABS(B24-'balance_raw_22460218'!$F$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_22460218'!$F$53,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_22460218'!$E$53="","—",IF(ABS(C24-'balance_raw_22460218'!$E$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_22460218'!$E$53,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_22460218'!$E$53="","—",IF(ABS(C24-'balance_raw_22460218'!$E$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_22460218'!$E$53,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_22460218'!$D$53="","—",IF(ABS(D24-'balance_raw_22460218'!$D$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_22460218'!$D$53,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_22460218'!$D$53="","—",IF(ABS(D24-'balance_raw_22460218'!$D$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_22460218'!$D$53,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -6906,15 +6906,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(B20-B24)&lt;=1,"✓ OK","❌ "&amp;TEXT(B20-B24,"+#,##0;-#,##0")&amp;" t.USD")</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(C20-C24)&lt;=1,"✓ OK","❌ "&amp;TEXT(C20-C24,"+#,##0;-#,##0")&amp;" t.USD")</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(D20-D24)&lt;=1,"✓ OK","❌ "&amp;TEXT(D20-D24,"+#,##0;-#,##0")&amp;" t.USD")</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -6930,15 +6930,15 @@
         </is>
       </c>
       <c r="B63" s="29">
-        <f>IF('res_raw_22460218'!$F$4="","—",IF(ABS(B7-'res_raw_22460218'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw_22460218'!$F$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_22460218'!$F$4="","—",IF(ABS(B7-'res_raw_22460218'!$F$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(B7-'res_raw_22460218'!$F$4,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C63" s="29">
-        <f>IF('res_raw_22460218'!$E$4="","—",IF(ABS(C7-'res_raw_22460218'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw_22460218'!$E$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_22460218'!$E$4="","—",IF(ABS(C7-'res_raw_22460218'!$E$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(C7-'res_raw_22460218'!$E$4,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D63" s="29">
-        <f>IF('res_raw_22460218'!$D$4="","—",IF(ABS(D7-'res_raw_22460218'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw_22460218'!$D$4,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_22460218'!$D$4="","—",IF(ABS(D7-'res_raw_22460218'!$D$4)&lt;=1,"✓ OK","❌ "&amp;TEXT(D7-'res_raw_22460218'!$D$4,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F63" s="25" t="inlineStr">
@@ -6954,15 +6954,15 @@
         </is>
       </c>
       <c r="B64" s="29">
-        <f>IF('res_raw_22460218'!$F$9="","—",IF(ABS(B12-'res_raw_22460218'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw_22460218'!$F$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_22460218'!$F$9="","—",IF(ABS(B12-'res_raw_22460218'!$F$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(B12-'res_raw_22460218'!$F$9,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C64" s="29">
-        <f>IF('res_raw_22460218'!$E$9="","—",IF(ABS(C12-'res_raw_22460218'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw_22460218'!$E$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_22460218'!$E$9="","—",IF(ABS(C12-'res_raw_22460218'!$E$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(C12-'res_raw_22460218'!$E$9,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF('res_raw_22460218'!$D$9="","—",IF(ABS(D12-'res_raw_22460218'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw_22460218'!$D$9,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_22460218'!$D$9="","—",IF(ABS(D12-'res_raw_22460218'!$D$9)&lt;=1,"✓ OK","❌ "&amp;TEXT(D12-'res_raw_22460218'!$D$9,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
@@ -6978,15 +6978,15 @@
         </is>
       </c>
       <c r="B65" s="29">
-        <f>IF('res_raw_22460218'!$F$14="","—",IF(ABS(B15-'res_raw_22460218'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw_22460218'!$F$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_22460218'!$F$14="","—",IF(ABS(B15-'res_raw_22460218'!$F$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(B15-'res_raw_22460218'!$F$14,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C65" s="29">
-        <f>IF('res_raw_22460218'!$E$14="","—",IF(ABS(C15-'res_raw_22460218'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw_22460218'!$E$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_22460218'!$E$14="","—",IF(ABS(C15-'res_raw_22460218'!$E$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(C15-'res_raw_22460218'!$E$14,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D65" s="29">
-        <f>IF('res_raw_22460218'!$D$14="","—",IF(ABS(D15-'res_raw_22460218'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw_22460218'!$D$14,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_22460218'!$D$14="","—",IF(ABS(D15-'res_raw_22460218'!$D$14)&lt;=1,"✓ OK","❌ "&amp;TEXT(D15-'res_raw_22460218'!$D$14,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F65" s="25" t="inlineStr">

--- a/filer/22460218_torm.xlsx
+++ b/filer/22460218_torm.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.USD)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.USD) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/22460218_torm.xlsx
+++ b/filer/22460218_torm.xlsx
@@ -202,8 +202,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +662,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +677,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1435,35 +1435,35 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
@@ -2625,35 +2625,35 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
@@ -2993,97 +2993,97 @@
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Hensættelse til udskudt skat</t>
-        </is>
-      </c>
-      <c r="B54" s="5">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B54" s="8">
         <f>'balance_raw_22460218'!$B$33</f>
         <v/>
       </c>
-      <c r="C54" s="5">
+      <c r="C54" s="8">
         <f>'balance_raw_22460218'!$C$33</f>
         <v/>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="8">
         <f>'balance_raw_22460218'!$D$33</f>
         <v/>
       </c>
-      <c r="E54" s="5">
+      <c r="E54" s="8">
         <f>'balance_raw_22460218'!$E$33</f>
         <v/>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="8">
         <f>'balance_raw_22460218'!$F$33</f>
         <v/>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" s="6">
+      <c r="H54" s="9">
         <f>IFERROR(B54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="I54" s="6">
+      <c r="I54" s="9">
         <f>IFERROR(C54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="J54" s="6">
+      <c r="J54" s="9">
         <f>IFERROR(D54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="K54" s="6">
+      <c r="K54" s="9">
         <f>IFERROR(E54/$B$54*100,"")</f>
         <v/>
       </c>
-      <c r="L54" s="6">
+      <c r="L54" s="9">
         <f>IFERROR(F54/$B$54*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B55" s="8">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B55" s="11">
         <f>'balance_raw_22460218'!$B$34</f>
         <v/>
       </c>
-      <c r="C55" s="8">
+      <c r="C55" s="11">
         <f>'balance_raw_22460218'!$C$34</f>
         <v/>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="11">
         <f>'balance_raw_22460218'!$D$34</f>
         <v/>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="11">
         <f>'balance_raw_22460218'!$E$34</f>
         <v/>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="11">
         <f>'balance_raw_22460218'!$F$34</f>
         <v/>
       </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" s="9">
+      <c r="H55" s="12">
         <f>IFERROR(B55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="12">
         <f>IFERROR(C55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="J55" s="9">
+      <c r="J55" s="12">
         <f>IFERROR(D55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="K55" s="9">
+      <c r="K55" s="12">
         <f>IFERROR(E55/$B$55*100,"")</f>
         <v/>
       </c>
-      <c r="L55" s="9">
+      <c r="L55" s="12">
         <f>IFERROR(F55/$B$55*100,"")</f>
         <v/>
       </c>
@@ -3091,7 +3091,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
+          <t>Langfristede lån</t>
         </is>
       </c>
       <c r="B56" s="5">
@@ -3139,7 +3139,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
+          <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
       <c r="B57" s="11">
@@ -3187,7 +3187,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
+          <t>Anden gæld (langfristet)</t>
         </is>
       </c>
       <c r="B58" s="5">
@@ -3233,97 +3233,97 @@
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B59" s="11">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B59" s="8">
         <f>'balance_raw_22460218'!$B$38</f>
         <v/>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="8">
         <f>'balance_raw_22460218'!$C$38</f>
         <v/>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="8">
         <f>'balance_raw_22460218'!$D$38</f>
         <v/>
       </c>
-      <c r="E59" s="11">
+      <c r="E59" s="8">
         <f>'balance_raw_22460218'!$E$38</f>
         <v/>
       </c>
-      <c r="F59" s="11">
+      <c r="F59" s="8">
         <f>'balance_raw_22460218'!$F$38</f>
         <v/>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" s="12">
+      <c r="H59" s="9">
         <f>IFERROR(B59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="I59" s="12">
+      <c r="I59" s="9">
         <f>IFERROR(C59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="J59" s="12">
+      <c r="J59" s="9">
         <f>IFERROR(D59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="K59" s="12">
+      <c r="K59" s="9">
         <f>IFERROR(E59/$B$59*100,"")</f>
         <v/>
       </c>
-      <c r="L59" s="12">
+      <c r="L59" s="9">
         <f>IFERROR(F59/$B$59*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B60" s="8">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B60" s="5">
         <f>'balance_raw_22460218'!$B$39</f>
         <v/>
       </c>
-      <c r="C60" s="8">
+      <c r="C60" s="5">
         <f>'balance_raw_22460218'!$C$39</f>
         <v/>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="5">
         <f>'balance_raw_22460218'!$D$39</f>
         <v/>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="5">
         <f>'balance_raw_22460218'!$E$39</f>
         <v/>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="5">
         <f>'balance_raw_22460218'!$F$39</f>
         <v/>
       </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" s="9">
+      <c r="H60" s="6">
         <f>IFERROR(B60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="6">
         <f>IFERROR(C60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="J60" s="9">
+      <c r="J60" s="6">
         <f>IFERROR(D60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="K60" s="9">
+      <c r="K60" s="6">
         <f>IFERROR(E60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="L60" s="9">
+      <c r="L60" s="6">
         <f>IFERROR(F60/$B$60*100,"")</f>
         <v/>
       </c>
@@ -3331,7 +3331,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B61" s="11">
@@ -3379,7 +3379,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B62" s="5">
@@ -3427,7 +3427,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B63" s="11">
@@ -3475,7 +3475,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3523,7 +3523,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B65" s="11">
@@ -3571,7 +3571,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B66" s="5">
@@ -3619,7 +3619,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B67" s="11">
@@ -3667,7 +3667,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
       <c r="B68" s="5">
@@ -3715,7 +3715,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
       <c r="B69" s="11">
@@ -3763,7 +3763,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
       <c r="B70" s="5">
@@ -3809,49 +3809,49 @@
       </c>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B71" s="11">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B71" s="8">
         <f>'balance_raw_22460218'!$B$50</f>
         <v/>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="8">
         <f>'balance_raw_22460218'!$C$50</f>
         <v/>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="8">
         <f>'balance_raw_22460218'!$D$50</f>
         <v/>
       </c>
-      <c r="E71" s="11">
+      <c r="E71" s="8">
         <f>'balance_raw_22460218'!$E$50</f>
         <v/>
       </c>
-      <c r="F71" s="11">
+      <c r="F71" s="8">
         <f>'balance_raw_22460218'!$F$50</f>
         <v/>
       </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" s="12">
+      <c r="H71" s="9">
         <f>IFERROR(B71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="I71" s="12">
+      <c r="I71" s="9">
         <f>IFERROR(C71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="J71" s="12">
+      <c r="J71" s="9">
         <f>IFERROR(D71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="K71" s="12">
+      <c r="K71" s="9">
         <f>IFERROR(E71/$B$71*100,"")</f>
         <v/>
       </c>
-      <c r="L71" s="12">
+      <c r="L71" s="9">
         <f>IFERROR(F71/$B$71*100,"")</f>
         <v/>
       </c>
@@ -3859,7 +3859,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Kortfristede gældsforpligtelser</t>
+          <t>Gældsforpligtelser</t>
         </is>
       </c>
       <c r="B72" s="8">
@@ -3907,7 +3907,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Gældsforpligtelser</t>
+          <t>Passiver</t>
         </is>
       </c>
       <c r="B73" s="8">
@@ -3952,100 +3952,100 @@
         <v/>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B74" s="8">
-        <f>'balance_raw_22460218'!$B$53</f>
-        <v/>
-      </c>
-      <c r="C74" s="8">
-        <f>'balance_raw_22460218'!$C$53</f>
-        <v/>
-      </c>
-      <c r="D74" s="8">
-        <f>'balance_raw_22460218'!$D$53</f>
-        <v/>
-      </c>
-      <c r="E74" s="8">
-        <f>'balance_raw_22460218'!$E$53</f>
-        <v/>
-      </c>
-      <c r="F74" s="8">
-        <f>'balance_raw_22460218'!$F$53</f>
-        <v/>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" s="9">
-        <f>IFERROR(B74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="I74" s="9">
-        <f>IFERROR(C74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="J74" s="9">
-        <f>IFERROR(D74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="K74" s="9">
-        <f>IFERROR(E74/$B$74*100,"")</f>
-        <v/>
-      </c>
-      <c r="L74" s="9">
-        <f>IFERROR(F74/$B$74*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>NØGLEOPLYSNINGER</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C76" s="3" t="n">
+      <c r="B75" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="C75" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="D75" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F76" s="3" t="n">
+      <c r="E75" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Gns. antal medarbejdere</t>
+        </is>
+      </c>
+      <c r="B76" s="5">
+        <f>'res_raw_22460218'!$B$17</f>
+        <v/>
+      </c>
+      <c r="C76" s="5">
+        <f>'res_raw_22460218'!$C$17</f>
+        <v/>
+      </c>
+      <c r="D76" s="5">
+        <f>'res_raw_22460218'!$D$17</f>
+        <v/>
+      </c>
+      <c r="E76" s="5">
+        <f>'res_raw_22460218'!$E$17</f>
+        <v/>
+      </c>
+      <c r="F76" s="5">
+        <f>'res_raw_22460218'!$F$17</f>
+        <v/>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" s="6">
+        <f>IFERROR(B76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="I76" s="6">
+        <f>IFERROR(C76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="J76" s="6">
+        <f>IFERROR(D76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="K76" s="6">
+        <f>IFERROR(E76/$B$76*100,"")</f>
+        <v/>
+      </c>
+      <c r="L76" s="6">
+        <f>IFERROR(F76/$B$76*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Gns. antal medarbejdere</t>
+          <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
       <c r="B77" s="11">
-        <f>'res_raw_22460218'!$B$17</f>
+        <f>'res_raw_22460218'!$B$18</f>
         <v/>
       </c>
       <c r="C77" s="11">
-        <f>'res_raw_22460218'!$C$17</f>
+        <f>'res_raw_22460218'!$C$18</f>
         <v/>
       </c>
       <c r="D77" s="11">
-        <f>'res_raw_22460218'!$D$17</f>
+        <f>'res_raw_22460218'!$D$18</f>
         <v/>
       </c>
       <c r="E77" s="11">
-        <f>'res_raw_22460218'!$E$17</f>
+        <f>'res_raw_22460218'!$E$18</f>
         <v/>
       </c>
       <c r="F77" s="11">
-        <f>'res_raw_22460218'!$F$17</f>
+        <f>'res_raw_22460218'!$F$18</f>
         <v/>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -4070,371 +4070,330 @@
         <v/>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B78" s="5">
-        <f>'res_raw_22460218'!$B$18</f>
-        <v/>
-      </c>
-      <c r="C78" s="5">
-        <f>'res_raw_22460218'!$C$18</f>
-        <v/>
-      </c>
-      <c r="D78" s="5">
-        <f>'res_raw_22460218'!$D$18</f>
-        <v/>
-      </c>
-      <c r="E78" s="5">
-        <f>'res_raw_22460218'!$E$18</f>
-        <v/>
-      </c>
-      <c r="F78" s="5">
-        <f>'res_raw_22460218'!$F$18</f>
-        <v/>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" s="6">
-        <f>IFERROR(B78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="I78" s="6">
-        <f>IFERROR(C78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="6">
-        <f>IFERROR(D78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="K78" s="6">
-        <f>IFERROR(E78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="L78" s="6">
-        <f>IFERROR(F78/$B$78*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>NØGLETAL</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C80" s="3" t="n">
+      <c r="B79" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="C79" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="D79" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="E79" s="3" t="n">
         <v>2024</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B80" s="13">
+        <f>IFERROR(($B$11+$B$13+$B$12)/$B$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="13">
+        <f>IFERROR(($C$11+$C$13+$C$12)/$C$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="13">
+        <f>IFERROR(($D$11+$D$13+$D$12)/$D$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="13">
+        <f>IFERROR(($E$11+$E$13+$E$12)/$E$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="13">
+        <f>IFERROR(($F$11+$F$13+$F$12)/$F$44*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B81" s="13">
-        <f>IFERROR(($B$11+$B$13+$B$12)/$B$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="C81" s="13">
-        <f>IFERROR(($C$11+$C$13+$C$12)/$C$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="13">
-        <f>IFERROR(($D$11+$D$13+$D$12)/$D$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="E81" s="13">
-        <f>IFERROR(($E$11+$E$13+$E$12)/$E$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="F81" s="13">
-        <f>IFERROR(($F$11+$F$13+$F$12)/$F$44*100,"")</f>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B81" s="14">
+        <f>IFERROR(($B$11+$B$13+$B$12)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="14">
+        <f>IFERROR(($C$11+$C$13+$C$12)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="14">
+        <f>IFERROR(($D$11+$D$13+$D$12)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="14">
+        <f>IFERROR(($E$11+$E$13+$E$12)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="14">
+        <f>IFERROR(($F$11+$F$13+$F$12)/$F$4*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B82" s="14">
-        <f>IFERROR(($B$11+$B$13+$B$12)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="14">
-        <f>IFERROR(($C$11+$C$13+$C$12)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="14">
-        <f>IFERROR(($D$11+$D$13+$D$12)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="14">
-        <f>IFERROR(($E$11+$E$13+$E$12)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="14">
-        <f>IFERROR(($F$11+$F$13+$F$12)/$F$4*100,"")</f>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B82" s="13">
+        <f>IFERROR($B$4/$B$44,"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="13">
+        <f>IFERROR($C$4/$C$44,"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="13">
+        <f>IFERROR($D$4/$D$44,"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="13">
+        <f>IFERROR($E$4/$E$44,"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="13">
+        <f>IFERROR($F$4/$F$44,"")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B83" s="13">
-        <f>IFERROR($B$4/$B$44,"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="13">
-        <f>IFERROR($C$4/$C$44,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="13">
-        <f>IFERROR($D$4/$D$44,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="13">
-        <f>IFERROR($E$4/$E$44,"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="13">
-        <f>IFERROR($F$4/$F$44,"")</f>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B83" s="14">
+        <f>IFERROR($B$16/$B$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="14">
+        <f>IFERROR($C$16/$C$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="14">
+        <f>IFERROR($D$16/$D$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="14">
+        <f>IFERROR($E$16/$E$53*100,"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="14">
+        <f>IFERROR($F$16/$F$53*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B84" s="14">
-        <f>IFERROR($B$16/$B$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="C84" s="14">
-        <f>IFERROR($C$16/$C$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="14">
-        <f>IFERROR($D$16/$D$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="14">
-        <f>IFERROR($E$16/$E$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="14">
-        <f>IFERROR($F$16/$F$53*100,"")</f>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B84" s="13">
+        <f>IFERROR($B$14/($B$73-$B$53)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="13">
+        <f>IFERROR($C$14/($C$73-$C$53)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="13">
+        <f>IFERROR($D$14/($D$73-$D$53)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="13">
+        <f>IFERROR($E$14/($E$73-$E$53)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="13">
+        <f>IFERROR($F$14/($F$73-$F$53)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B85" s="13">
-        <f>IFERROR($B$14/($B$74-$B$53)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C85" s="13">
-        <f>IFERROR($C$14/($C$74-$C$53)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="13">
-        <f>IFERROR($D$14/($D$74-$D$53)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="13">
-        <f>IFERROR($E$14/($E$74-$E$53)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F85" s="13">
-        <f>IFERROR($F$14/($F$74-$F$53)*100,"")</f>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B85" s="14">
+        <f>IFERROR($B$53/$B$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="14">
+        <f>IFERROR($C$53/$C$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="14">
+        <f>IFERROR($D$53/$D$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="14">
+        <f>IFERROR($E$53/$E$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="14">
+        <f>IFERROR($F$53/$F$44*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B86" s="14">
-        <f>IFERROR($B$53/$B$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="C86" s="14">
-        <f>IFERROR($C$53/$C$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="D86" s="14">
-        <f>IFERROR($D$53/$D$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="E86" s="14">
-        <f>IFERROR($E$53/$E$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="F86" s="14">
-        <f>IFERROR($F$53/$F$44*100,"")</f>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B86" s="13">
+        <f>IFERROR(($B$73-$B$53)/$B$53,"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="13">
+        <f>IFERROR(($C$73-$C$53)/$C$53,"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="13">
+        <f>IFERROR(($D$73-$D$53)/$D$53,"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="13">
+        <f>IFERROR(($E$73-$E$53)/$E$53,"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="13">
+        <f>IFERROR(($F$73-$F$53)/$F$53,"")</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B87" s="13">
-        <f>IFERROR(($B$74-$B$53)/$B$53,"")</f>
-        <v/>
-      </c>
-      <c r="C87" s="13">
-        <f>IFERROR(($C$74-$C$53)/$C$53,"")</f>
-        <v/>
-      </c>
-      <c r="D87" s="13">
-        <f>IFERROR(($D$74-$D$53)/$D$53,"")</f>
-        <v/>
-      </c>
-      <c r="E87" s="13">
-        <f>IFERROR(($E$74-$E$53)/$E$53,"")</f>
-        <v/>
-      </c>
-      <c r="F87" s="13">
-        <f>IFERROR(($F$74-$F$53)/$F$53,"")</f>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B87" s="14">
+        <f>IFERROR($B$43/$B$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="14">
+        <f>IFERROR($C$43/$C$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="14">
+        <f>IFERROR($D$43/$D$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="14">
+        <f>IFERROR($E$43/$E$71*100,"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="14">
+        <f>IFERROR($F$43/$F$71*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B88" s="14">
-        <f>IFERROR($B$43/$B$72*100,"")</f>
-        <v/>
-      </c>
-      <c r="C88" s="14">
-        <f>IFERROR($C$43/$C$72*100,"")</f>
-        <v/>
-      </c>
-      <c r="D88" s="14">
-        <f>IFERROR($D$43/$D$72*100,"")</f>
-        <v/>
-      </c>
-      <c r="E88" s="14">
-        <f>IFERROR($E$43/$E$72*100,"")</f>
-        <v/>
-      </c>
-      <c r="F88" s="14">
-        <f>IFERROR($F$43/$F$72*100,"")</f>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B88" s="13">
+        <f>IFERROR(B80-B84,"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="13">
+        <f>IFERROR(C80-C84,"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="13">
+        <f>IFERROR(D80-D84,"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="13">
+        <f>IFERROR(E80-E84,"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="13">
+        <f>IFERROR(F80-F84,"")</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B89" s="13">
-        <f>IFERROR(B81-B85,"")</f>
-        <v/>
-      </c>
-      <c r="C89" s="13">
-        <f>IFERROR(C81-C85,"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="13">
-        <f>IFERROR(D81-D85,"")</f>
-        <v/>
-      </c>
-      <c r="E89" s="13">
-        <f>IFERROR(E81-E85,"")</f>
-        <v/>
-      </c>
-      <c r="F89" s="13">
-        <f>IFERROR(F81-F85,"")</f>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B89" s="14">
+        <f>IFERROR(($B$73-$B$53)/$B$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="14">
+        <f>IFERROR(($C$73-$C$53)/$C$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="14">
+        <f>IFERROR(($D$73-$D$53)/$D$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="14">
+        <f>IFERROR(($E$73-$E$53)/$E$44*100,"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="14">
+        <f>IFERROR(($F$73-$F$53)/$F$44*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B90" s="14">
-        <f>IFERROR(($B$74-$B$53)/$B$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="C90" s="14">
-        <f>IFERROR(($C$74-$C$53)/$C$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="D90" s="14">
-        <f>IFERROR(($D$74-$D$53)/$D$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="E90" s="14">
-        <f>IFERROR(($E$74-$E$53)/$E$44*100,"")</f>
-        <v/>
-      </c>
-      <c r="F90" s="14">
-        <f>IFERROR(($F$74-$F$53)/$F$44*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="10" t="inlineStr">
-        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B91" s="13">
-        <f>IFERROR($B$31/($B$53+$B$60)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C91" s="13">
-        <f>IFERROR($C$31/($C$53+$C$60)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="13">
-        <f>IFERROR($D$31/($D$53+$D$60)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E91" s="13">
-        <f>IFERROR($E$31/($E$53+$E$60)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F91" s="13">
-        <f>IFERROR($F$31/($F$53+$F$60)*100,"")</f>
-        <v/>
+      <c r="B90" s="13">
+        <f>IFERROR($B$31/($B$53+$B$59)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="13">
+        <f>IFERROR($C$31/($C$53+$C$59)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="13">
+        <f>IFERROR($D$31/($D$53+$D$59)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="13">
+        <f>IFERROR($E$31/($E$53+$E$59)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F90" s="13">
+        <f>IFERROR($F$31/($F$53+$F$59)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4466,19 +4425,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4488,19 +4447,19 @@
         </is>
       </c>
       <c r="B2" s="16" t="n">
-        <v>739360</v>
+        <v>619000</v>
       </c>
       <c r="C2" s="16" t="n">
-        <v>619000</v>
+        <v>1440000</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1440000</v>
+        <v>1481363</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>1481363</v>
+        <v>1463625</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>1463625</v>
+        <v>1018993</v>
       </c>
     </row>
     <row r="3">
@@ -4521,18 +4480,20 @@
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
+      <c r="B4" s="16" t="n">
+        <v>127460</v>
+      </c>
       <c r="C4" s="16" t="n">
-        <v>127460</v>
+        <v>743708</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>743708</v>
+        <v>720935</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>720935</v>
+        <v>639096</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>639096</v>
+        <v>387980</v>
       </c>
     </row>
     <row r="5">
@@ -4554,19 +4515,19 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>35470</v>
+        <v>35023</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>35023</v>
+        <v>32837</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>32837</v>
+        <v>49579</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>49579</v>
+        <v>55899</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>55899</v>
+        <v>61070</v>
       </c>
     </row>
     <row r="7">
@@ -4576,19 +4537,19 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>625</v>
+        <v>8214</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>8214</v>
+        <v>74521</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>74521</v>
+        <v>283840</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>283840</v>
+        <v>6728</v>
       </c>
     </row>
     <row r="8">
@@ -4598,19 +4559,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>208372</v>
+        <v>16704</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>16704</v>
+        <v>11325</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>11325</v>
+        <v>13655</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>13655</v>
+        <v>22257</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>22257</v>
+        <v>27099</v>
       </c>
     </row>
     <row r="9">
@@ -4620,19 +4581,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>-63835</v>
+        <v>45000</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>45000</v>
+        <v>587000</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>587000</v>
+        <v>597072</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>597072</v>
+        <v>707220</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>707220</v>
+        <v>119221</v>
       </c>
     </row>
     <row r="10">
@@ -4642,19 +4603,19 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>20563</v>
+        <v>19054</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>19054</v>
+        <v>8129</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>8129</v>
+        <v>20515</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>20515</v>
+        <v>307852</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>307852</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="11">
@@ -4664,19 +4625,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>9666</v>
+        <v>341</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>341</v>
+        <v>5465</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>5465</v>
+        <v>34894</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>34894</v>
+        <v>15112</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>15112</v>
+        <v>10611</v>
       </c>
     </row>
     <row r="12">
@@ -4686,19 +4647,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>40564</v>
+        <v>30762</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>30762</v>
+        <v>60184</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>60184</v>
+        <v>80959</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>80959</v>
+        <v>48160</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>48160</v>
+        <v>29531</v>
       </c>
     </row>
     <row r="13">
@@ -4708,14 +4669,12 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>-31000</v>
+        <v>-30000</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>-30000</v>
-      </c>
-      <c r="D13" s="16" t="n">
         <v>-55000</v>
       </c>
+      <c r="D13" s="16" t="n"/>
       <c r="E13" s="16" t="n"/>
       <c r="F13" s="16" t="n"/>
     </row>
@@ -4726,19 +4685,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>-89942</v>
+        <v>26406</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>26406</v>
+        <v>544685</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>544685</v>
+        <v>571522</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>571522</v>
+        <v>982024</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>982024</v>
+        <v>101318</v>
       </c>
     </row>
     <row r="15">
@@ -4748,19 +4707,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>896</v>
+        <v>1193</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>1193</v>
+        <v>1087</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>1087</v>
+        <v>1351</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>1351</v>
+        <v>775</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>775</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="16">
@@ -4770,19 +4729,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>-90838</v>
+        <v>25213</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>25213</v>
+        <v>543598</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>543598</v>
+        <v>570171</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>570171</v>
+        <v>981249</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>981249</v>
+        <v>100258</v>
       </c>
     </row>
     <row r="17">
@@ -4792,14 +4751,12 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>243</v>
-      </c>
-      <c r="D17" s="16" t="n">
         <v>227</v>
       </c>
+      <c r="D17" s="16" t="n"/>
       <c r="E17" s="16" t="n"/>
       <c r="F17" s="16" t="n"/>
     </row>
@@ -4810,14 +4767,12 @@
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>904000</v>
+        <v>643000</v>
       </c>
       <c r="C18" s="16" t="n">
-        <v>643000</v>
-      </c>
-      <c r="D18" s="16" t="n">
         <v>153000</v>
       </c>
+      <c r="D18" s="16" t="n"/>
       <c r="E18" s="16" t="n"/>
       <c r="F18" s="16" t="n"/>
     </row>
@@ -4832,7 +4787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4850,19 +4805,19 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
@@ -4871,18 +4826,20 @@
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n"/>
+      <c r="B2" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="C2" s="16" t="n">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="D2" s="16" t="n">
-        <v>651</v>
+        <v>792</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>792</v>
+        <v>1006</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>1006</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="3">
@@ -4891,18 +4848,20 @@
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
+      <c r="B3" s="16" t="n">
+        <v>2934</v>
+      </c>
       <c r="C3" s="16" t="n">
-        <v>2934</v>
+        <v>1842</v>
       </c>
       <c r="D3" s="16" t="n">
-        <v>1842</v>
+        <v>757</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>757</v>
+        <v>5245</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>5245</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="4">
@@ -4911,18 +4870,20 @@
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
+      <c r="B4" s="16" t="n">
+        <v>4850</v>
+      </c>
       <c r="C4" s="16" t="n">
-        <v>4850</v>
+        <v>2926</v>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2926</v>
+        <v>2285</v>
       </c>
       <c r="E4" s="16" t="n">
-        <v>2285</v>
+        <v>1098</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>1098</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5">
@@ -4931,9 +4892,7 @@
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>5012</v>
-      </c>
+      <c r="B5" s="16" t="n"/>
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
@@ -4958,14 +4917,12 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>12024</v>
+        <v>11996</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>11996</v>
-      </c>
-      <c r="D7" s="16" t="n">
         <v>0</v>
       </c>
+      <c r="D7" s="16" t="n"/>
       <c r="E7" s="16" t="n"/>
       <c r="F7" s="16" t="n"/>
     </row>
@@ -4976,19 +4933,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>1057690</v>
+        <v>1663731</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>1663731</v>
+        <v>1618912</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>1618912</v>
+        <v>1696527</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>1696527</v>
+        <v>1636247</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>1636247</v>
+        <v>1392728</v>
       </c>
     </row>
     <row r="9">
@@ -4998,19 +4955,19 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>804404</v>
+        <v>126261</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>126261</v>
+        <v>128429</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>128429</v>
+        <v>179033</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>179033</v>
+        <v>6810</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>6810</v>
+        <v>12410</v>
       </c>
     </row>
     <row r="10">
@@ -5032,19 +4989,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>805992</v>
+        <v>127734</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>127734</v>
+        <v>128701</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>128701</v>
+        <v>179109</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>179109</v>
+        <v>6886</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>6886</v>
+        <v>12410</v>
       </c>
     </row>
     <row r="12">
@@ -5054,19 +5011,19 @@
         </is>
       </c>
       <c r="B12" s="16" t="n">
-        <v>1863682</v>
+        <v>1791465</v>
       </c>
       <c r="C12" s="16" t="n">
-        <v>1791465</v>
+        <v>1748264</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1748264</v>
+        <v>1876428</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>1876428</v>
+        <v>1644139</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>1644139</v>
+        <v>1406664</v>
       </c>
     </row>
     <row r="13">
@@ -5076,19 +5033,19 @@
         </is>
       </c>
       <c r="B13" s="16" t="n">
-        <v>22306</v>
+        <v>48658</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>48658</v>
+        <v>60991</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>60991</v>
+        <v>57400</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>57400</v>
+        <v>55047</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>55047</v>
+        <v>49620</v>
       </c>
     </row>
     <row r="14">
@@ -5098,19 +5055,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>57080</v>
+        <v>83218</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>83218</v>
+        <v>255618</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>255618</v>
+        <v>193525</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>193525</v>
+        <v>128885</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>128885</v>
+        <v>130463</v>
       </c>
     </row>
     <row r="15">
@@ -5120,19 +5077,19 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>43568</v>
+        <v>5039</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>5039</v>
+        <v>93</v>
       </c>
       <c r="D15" s="16" t="n">
-        <v>93</v>
+        <v>66747</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>66747</v>
+        <v>3139</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>3139</v>
+        <v>15047</v>
       </c>
     </row>
     <row r="16">
@@ -5142,19 +5099,19 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>22780</v>
+        <v>31123</v>
       </c>
       <c r="C16" s="16" t="n">
-        <v>31123</v>
+        <v>16983</v>
       </c>
       <c r="D16" s="16" t="n">
-        <v>16983</v>
+        <v>21748</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>21748</v>
+        <v>28762</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>28762</v>
+        <v>8049</v>
       </c>
     </row>
     <row r="17">
@@ -5164,19 +5121,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>1791</v>
+        <v>4981</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>4981</v>
+        <v>9147</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>9147</v>
+        <v>8738</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>8738</v>
+        <v>10034</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>10034</v>
+        <v>36523</v>
       </c>
     </row>
     <row r="18">
@@ -5246,19 +5203,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>57635</v>
+        <v>143840</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>143840</v>
+        <v>296863</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>296863</v>
+        <v>262989</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>262989</v>
+        <v>169449</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>169449</v>
+        <v>128235</v>
       </c>
     </row>
     <row r="24">
@@ -5268,19 +5225,19 @@
         </is>
       </c>
       <c r="B24" s="16" t="n">
-        <v>205160</v>
+        <v>316859</v>
       </c>
       <c r="C24" s="16" t="n">
-        <v>316859</v>
+        <v>639695</v>
       </c>
       <c r="D24" s="16" t="n">
-        <v>639695</v>
+        <v>611147</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>611147</v>
+        <v>395316</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>395316</v>
+        <v>367937</v>
       </c>
     </row>
     <row r="25">
@@ -5290,19 +5247,19 @@
         </is>
       </c>
       <c r="B25" s="16" t="n">
-        <v>2068842</v>
+        <v>2108000</v>
       </c>
       <c r="C25" s="16" t="n">
-        <v>2108000</v>
+        <v>2388000</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2388000</v>
+        <v>2487575</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>2487575</v>
+        <v>2039455</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>2039455</v>
+        <v>1774601</v>
       </c>
     </row>
     <row r="26">
@@ -5321,7 +5278,7 @@
         <v>141946</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>141946</v>
+        <v>180773</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>180773</v>
@@ -5370,7 +5327,7 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>809</v>
+        <v>5896</v>
       </c>
       <c r="C30" s="16" t="n">
         <v>5896</v>
@@ -5392,19 +5349,19 @@
         </is>
       </c>
       <c r="B31" s="16" t="n">
-        <v>371078</v>
+        <v>397884</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>397884</v>
+        <v>943037</v>
       </c>
       <c r="D31" s="16" t="n">
-        <v>943037</v>
+        <v>1411890</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>1411890</v>
+        <v>1139987</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>1139987</v>
+        <v>1264116</v>
       </c>
     </row>
     <row r="32">
@@ -5414,143 +5371,139 @@
         </is>
       </c>
       <c r="B32" s="16" t="n">
-        <v>519729</v>
+        <v>544000</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>544000</v>
+        <v>1091000</v>
       </c>
       <c r="D32" s="16" t="n">
-        <v>1091000</v>
+        <v>1559777</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>1559777</v>
+        <v>1324484</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>1324484</v>
+        <v>1451569</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Hensættelse til udskudt skat</t>
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
         </is>
       </c>
       <c r="B33" s="16" t="n">
-        <v>45176</v>
-      </c>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
+        <v>18300</v>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>6500</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="16" t="n"/>
       <c r="F33" s="16" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n">
-        <v>45176</v>
-      </c>
-      <c r="C34" s="16" t="n">
-        <v>18300</v>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
       <c r="F34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="n">
+        <v>440815</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>484030</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <v>496369</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>444362</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>27113</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>165064</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>440815</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>484030</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>496369</v>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>444362</v>
-      </c>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>806276</v>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="D37" s="16" t="n"/>
       <c r="E37" s="16" t="n"/>
       <c r="F37" s="16" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n"/>
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n">
+        <v>1292267</v>
+      </c>
       <c r="C38" s="16" t="n">
-        <v>806276</v>
+        <v>531356</v>
       </c>
       <c r="D38" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+        <v>543806</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>491854</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>74895</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>165064</v>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>1292267</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>531356</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>543806</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>491854</v>
-      </c>
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B40" s="16" t="n"/>
@@ -5562,241 +5515,227 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="n">
+        <v>41785</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>50125</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>71318</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>57200</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>161129</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>15499</v>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>41785</v>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>50125</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>71318</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>57200</v>
-      </c>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n">
+        <v>34587</v>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>45739</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>37901</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <v>39522</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>29116</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B44" s="16" t="n">
-        <v>14027</v>
+        <v>149351</v>
       </c>
       <c r="C44" s="16" t="n">
-        <v>34587</v>
+        <v>639059</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>45739</v>
+        <v>235563</v>
       </c>
       <c r="E44" s="16" t="n">
-        <v>37901</v>
+        <v>76097</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>39522</v>
+        <v>8607</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>1260329</v>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>149351</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>639059</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>235563</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>76097</v>
-      </c>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B46" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <v>801</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="16" t="n"/>
       <c r="F46" s="16" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>155</v>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>801</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>0</v>
-      </c>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
       <c r="F47" s="16" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B48" s="16" t="n">
+        <v>27831</v>
+      </c>
+      <c r="C48" s="16" t="n">
+        <v>23114</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <v>36513</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>49285</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n">
-        <v>30563</v>
-      </c>
-      <c r="C49" s="16" t="n">
-        <v>27831</v>
-      </c>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="16" t="n"/>
       <c r="D49" s="16" t="n">
-        <v>23114</v>
+        <v>2697</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>36513</v>
+        <v>4015</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>46283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B50" s="16" t="n">
-        <v>18300</v>
-      </c>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
+        <v>253565</v>
+      </c>
+      <c r="C50" s="16" t="n">
+        <v>758838</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <v>383992</v>
+      </c>
       <c r="E50" s="16" t="n">
-        <v>2697</v>
+        <v>223117</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>4015</v>
+        <v>248137</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>Kortfristede gældsforpligtelser</t>
+          <t>Gældsforpligtelser</t>
         </is>
       </c>
       <c r="B51" s="16" t="n">
-        <v>1338873</v>
+        <v>1564132</v>
       </c>
       <c r="C51" s="16" t="n">
-        <v>253565</v>
+        <v>1296694</v>
       </c>
       <c r="D51" s="16" t="n">
-        <v>758838</v>
+        <v>927796</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>383992</v>
+        <v>714971</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>223117</v>
+        <v>323032</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>Gældsforpligtelser</t>
+          <t>Passiver</t>
         </is>
       </c>
       <c r="B52" s="16" t="n">
-        <v>1549113</v>
+        <v>2108324</v>
       </c>
       <c r="C52" s="16" t="n">
-        <v>1564132</v>
+        <v>2387959</v>
       </c>
       <c r="D52" s="16" t="n">
-        <v>1296694</v>
+        <v>2487575</v>
       </c>
       <c r="E52" s="16" t="n">
-        <v>927796</v>
+        <v>2039455</v>
       </c>
       <c r="F52" s="16" t="n">
-        <v>714971</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n">
-        <v>2068842</v>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>2108324</v>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>2387959</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>2487575</v>
-      </c>
-      <c r="F53" s="16" t="n">
-        <v>2039455</v>
+        <v>1774601</v>
       </c>
     </row>
   </sheetData>
@@ -5835,13 +5774,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6252,15 +6191,15 @@
         </is>
       </c>
       <c r="B23" s="24">
-        <f>'balance_raw_22460218'!$F$53-'balance_raw_22460218'!$F$32</f>
+        <f>'balance_raw_22460218'!$F$52-'balance_raw_22460218'!$F$32</f>
         <v/>
       </c>
       <c r="C23" s="24">
-        <f>'balance_raw_22460218'!$E$53-'balance_raw_22460218'!$E$32</f>
+        <f>'balance_raw_22460218'!$E$52-'balance_raw_22460218'!$E$32</f>
         <v/>
       </c>
       <c r="D23" s="24">
-        <f>'balance_raw_22460218'!$D$53-'balance_raw_22460218'!$D$32</f>
+        <f>'balance_raw_22460218'!$D$52-'balance_raw_22460218'!$D$32</f>
         <v/>
       </c>
       <c r="F23" s="25" t="inlineStr">
@@ -6366,15 +6305,15 @@
         </is>
       </c>
       <c r="B29" s="24">
-        <f>'balance_raw_22460218'!$F$51</f>
+        <f>'balance_raw_22460218'!$F$50</f>
         <v/>
       </c>
       <c r="C29" s="24">
-        <f>'balance_raw_22460218'!$E$51</f>
+        <f>'balance_raw_22460218'!$E$50</f>
         <v/>
       </c>
       <c r="D29" s="24">
-        <f>'balance_raw_22460218'!$D$51</f>
+        <f>'balance_raw_22460218'!$D$50</f>
         <v/>
       </c>
       <c r="F29" s="25" t="inlineStr">
@@ -6531,7 +6470,7 @@
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -6649,7 +6588,7 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -6825,7 +6764,7 @@
     <row r="57">
       <c r="A57" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B57" s="29" t="n"/>
@@ -6882,15 +6821,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_22460218'!$F$53="","—",IF(ABS(B24-'balance_raw_22460218'!$F$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_22460218'!$F$53,"+#,##0;-#,##0")&amp;" t.USD"))</f>
+        <f>IF('balance_raw_22460218'!$F$52="","—",IF(ABS(B24-'balance_raw_22460218'!$F$52)&lt;=1,"✓ OK","❌ "&amp;TEXT(B24-'balance_raw_22460218'!$F$52,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_22460218'!$E$53="","—",IF(ABS(C24-'balance_raw_22460218'!$E$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_22460218'!$E$53,"+#,##0;-#,##0")&amp;" t.USD"))</f>
+        <f>IF('balance_raw_22460218'!$E$52="","—",IF(ABS(C24-'balance_raw_22460218'!$E$52)&lt;=1,"✓ OK","❌ "&amp;TEXT(C24-'balance_raw_22460218'!$E$52,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_22460218'!$D$53="","—",IF(ABS(D24-'balance_raw_22460218'!$D$53)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_22460218'!$D$53,"+#,##0;-#,##0")&amp;" t.USD"))</f>
+        <f>IF('balance_raw_22460218'!$D$52="","—",IF(ABS(D24-'balance_raw_22460218'!$D$52)&lt;=1,"✓ OK","❌ "&amp;TEXT(D24-'balance_raw_22460218'!$D$52,"+#,##0;-#,##0")&amp;" t.USD"))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -7048,27 +6987,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7095,10 +7034,10 @@
       </c>
       <c r="D3" s="35" t="n"/>
       <c r="E3" s="35" t="n"/>
-      <c r="F3" s="35" t="n"/>
-      <c r="G3" s="35" t="n">
+      <c r="F3" s="35" t="n">
         <v>117125</v>
       </c>
+      <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
         <is>
@@ -7122,18 +7061,20 @@
           <t>fsa:HedgeFund</t>
         </is>
       </c>
-      <c r="D4" s="38" t="n"/>
+      <c r="D4" s="38" t="n">
+        <v>-1534</v>
+      </c>
       <c r="E4" s="38" t="n">
-        <v>-1534</v>
+        <v>386</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>386</v>
+        <v>45</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>45</v>
+        <v>-2172</v>
       </c>
       <c r="H4" s="38" t="n">
-        <v>-2172</v>
+        <v>784</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7157,16 +7098,16 @@
           <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
         </is>
       </c>
-      <c r="D5" s="35" t="n"/>
+      <c r="D5" s="35" t="n">
+        <v>-104</v>
+      </c>
       <c r="E5" s="35" t="n">
-        <v>-104</v>
+        <v>153</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>153</v>
-      </c>
-      <c r="G5" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="G5" s="35" t="n"/>
       <c r="H5" s="35" t="n"/>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7190,9 +7131,11 @@
           <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n"/>
+      <c r="D6" s="38" t="n">
+        <v>1473</v>
+      </c>
       <c r="E6" s="38" t="n">
-        <v>1473</v>
+        <v>76</v>
       </c>
       <c r="F6" s="38" t="n">
         <v>76</v>
@@ -7201,7 +7144,7 @@
         <v>76</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
@@ -7225,7 +7168,9 @@
           <t>fsa:LongtermTaxPayables</t>
         </is>
       </c>
-      <c r="D7" s="35" t="n"/>
+      <c r="D7" s="35" t="n">
+        <v>45176</v>
+      </c>
       <c r="E7" s="35" t="n">
         <v>45176</v>
       </c>
@@ -7260,18 +7205,20 @@
           <t>fsa:Ships</t>
         </is>
       </c>
-      <c r="D8" s="38" t="n"/>
+      <c r="D8" s="38" t="n">
+        <v>1643951</v>
+      </c>
       <c r="E8" s="38" t="n">
-        <v>1643951</v>
+        <v>1614144</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>1614144</v>
+        <v>1693485</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>1693485</v>
+        <v>1629904</v>
       </c>
       <c r="H8" s="38" t="n">
-        <v>1629904</v>
+        <v>1388275</v>
       </c>
       <c r="I8" s="39" t="inlineStr">
         <is>
